--- a/static/excel_files/NA_WIN.xlsx
+++ b/static/excel_files/NA_WIN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jesusalberca/Desktop/qc_matrix_generator/static/excel_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A606F503-EF04-B249-A3E6-BEA23EE69BDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F57F059-FE8B-3448-B9E7-6615C90757FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20540" yWindow="660" windowWidth="30480" windowHeight="20780" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -808,8 +808,8 @@
     <col min="2" max="2" width="14.33203125" customWidth="1"/>
     <col min="3" max="3" width="19.6640625" customWidth="1"/>
     <col min="4" max="4" width="16.83203125" customWidth="1"/>
-    <col min="5" max="5" width="19.6640625" customWidth="1"/>
-    <col min="6" max="6" width="78.6640625" customWidth="1"/>
+    <col min="5" max="5" width="66.5" customWidth="1"/>
+    <col min="6" max="6" width="52.6640625" customWidth="1"/>
     <col min="7" max="8" width="24.1640625" customWidth="1"/>
     <col min="9" max="9" width="16.33203125" customWidth="1"/>
     <col min="10" max="10" width="16.6640625" customWidth="1"/>
@@ -862,18 +862,18 @@
         <v>4</v>
       </c>
       <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="F2" s="3"/>
       <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="5"/>
       <c r="K2" s="5"/>
       <c r="L2" s="5"/>
     </row>
@@ -885,18 +885,18 @@
         <v>4</v>
       </c>
       <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="5" t="s">
+      <c r="E3" s="5" t="s">
         <v>9</v>
       </c>
+      <c r="F3" s="5"/>
       <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="6" t="s">
+      <c r="H3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J3" s="5"/>
       <c r="K3" s="5"/>
       <c r="L3" s="5"/>
     </row>
@@ -908,18 +908,18 @@
         <v>4</v>
       </c>
       <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="F4" s="3"/>
       <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J4" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J4" s="3"/>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
     </row>
@@ -931,18 +931,18 @@
         <v>4</v>
       </c>
       <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="5" t="s">
+      <c r="E5" s="5" t="s">
         <v>13</v>
       </c>
+      <c r="F5" s="5"/>
       <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="6" t="s">
+      <c r="H5" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J5" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J5" s="5"/>
       <c r="K5" s="5"/>
       <c r="L5" s="5"/>
     </row>
@@ -954,18 +954,18 @@
         <v>4</v>
       </c>
       <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="3" t="s">
+      <c r="E6" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="F6" s="3"/>
       <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="1" t="s">
+      <c r="H6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J6" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J6" s="5"/>
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
     </row>
@@ -977,18 +977,18 @@
         <v>4</v>
       </c>
       <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="5" t="s">
+      <c r="E7" s="5" t="s">
         <v>15</v>
       </c>
+      <c r="F7" s="5"/>
       <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="6" t="s">
+      <c r="H7" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J7" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J7" s="3"/>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
     </row>
@@ -1000,18 +1000,18 @@
         <v>4</v>
       </c>
       <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="3" t="s">
+      <c r="E8" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="F8" s="3"/>
       <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="1" t="s">
+      <c r="H8" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J8" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J8" s="5"/>
       <c r="K8" s="5"/>
       <c r="L8" s="5"/>
     </row>
@@ -1023,18 +1023,18 @@
         <v>4</v>
       </c>
       <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="5" t="s">
+      <c r="E9" s="5" t="s">
         <v>17</v>
       </c>
+      <c r="F9" s="5"/>
       <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="6" t="s">
+      <c r="H9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J9" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J9" s="3"/>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
     </row>
@@ -1046,18 +1046,18 @@
         <v>18</v>
       </c>
       <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="3" t="s">
+      <c r="E10" s="3" t="s">
         <v>19</v>
       </c>
+      <c r="F10" s="3"/>
       <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="1" t="s">
+      <c r="H10" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J10" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J10" s="5"/>
       <c r="K10" s="5"/>
       <c r="L10" s="5"/>
     </row>
@@ -1069,18 +1069,18 @@
         <v>18</v>
       </c>
       <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="5" t="s">
+      <c r="E11" s="5" t="s">
         <v>20</v>
       </c>
+      <c r="F11" s="5"/>
       <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="6" t="s">
+      <c r="H11" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="J11" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I11" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
     </row>
@@ -1092,18 +1092,18 @@
         <v>18</v>
       </c>
       <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="3" t="s">
+      <c r="E12" s="3" t="s">
         <v>21</v>
       </c>
+      <c r="F12" s="3"/>
       <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="1" t="s">
+      <c r="H12" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J12" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I12" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J12" s="5"/>
       <c r="K12" s="5"/>
       <c r="L12" s="5"/>
     </row>
@@ -1115,18 +1115,18 @@
         <v>18</v>
       </c>
       <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="5" t="s">
+      <c r="E13" s="5" t="s">
         <v>22</v>
       </c>
+      <c r="F13" s="5"/>
       <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="6" t="s">
+      <c r="H13" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="J13" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I13" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J13" s="3"/>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
     </row>
@@ -1138,18 +1138,18 @@
         <v>18</v>
       </c>
       <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="3" t="s">
+      <c r="E14" s="3" t="s">
         <v>23</v>
       </c>
+      <c r="F14" s="3"/>
       <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="1" t="s">
+      <c r="H14" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J14" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I14" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J14" s="5"/>
       <c r="K14" s="5"/>
       <c r="L14" s="5"/>
     </row>
@@ -1161,18 +1161,18 @@
         <v>18</v>
       </c>
       <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="5" t="s">
+      <c r="E15" s="5" t="s">
         <v>24</v>
       </c>
+      <c r="F15" s="5"/>
       <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="6" t="s">
+      <c r="H15" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="J15" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I15" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J15" s="5"/>
       <c r="K15" s="5"/>
       <c r="L15" s="5"/>
     </row>
@@ -1184,18 +1184,18 @@
         <v>18</v>
       </c>
       <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="3" t="s">
+      <c r="E16" s="3" t="s">
         <v>25</v>
       </c>
+      <c r="F16" s="3"/>
       <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="1" t="s">
+      <c r="H16" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J16" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I16" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J16" s="5"/>
       <c r="K16" s="5"/>
       <c r="L16" s="5"/>
     </row>
@@ -1207,18 +1207,18 @@
         <v>18</v>
       </c>
       <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="5" t="s">
+      <c r="E17" s="5" t="s">
         <v>26</v>
       </c>
+      <c r="F17" s="5"/>
       <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-      <c r="I17" s="6" t="s">
+      <c r="H17" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="J17" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I17" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J17" s="5"/>
       <c r="K17" s="5"/>
       <c r="L17" s="5"/>
     </row>
@@ -1230,18 +1230,18 @@
         <v>18</v>
       </c>
       <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="3" t="s">
+      <c r="E18" s="3" t="s">
         <v>27</v>
       </c>
+      <c r="F18" s="3"/>
       <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="1" t="s">
+      <c r="H18" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J18" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I18" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J18" s="5"/>
       <c r="K18" s="5"/>
       <c r="L18" s="5"/>
     </row>
@@ -1253,18 +1253,18 @@
         <v>18</v>
       </c>
       <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="5" t="s">
+      <c r="E19" s="5" t="s">
         <v>27</v>
       </c>
+      <c r="F19" s="5"/>
       <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
-      <c r="I19" s="6" t="s">
+      <c r="H19" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="J19" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I19" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
     </row>
@@ -1276,18 +1276,18 @@
         <v>18</v>
       </c>
       <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="3" t="s">
+      <c r="E20" s="3" t="s">
         <v>28</v>
       </c>
+      <c r="F20" s="3"/>
       <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="1" t="s">
+      <c r="H20" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J20" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I20" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J20" s="5"/>
       <c r="K20" s="5"/>
       <c r="L20" s="5"/>
     </row>
@@ -1299,18 +1299,18 @@
         <v>18</v>
       </c>
       <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="5" t="s">
+      <c r="E21" s="5" t="s">
         <v>29</v>
       </c>
+      <c r="F21" s="5"/>
       <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
-      <c r="I21" s="6" t="s">
+      <c r="H21" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="J21" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I21" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J21" s="5"/>
       <c r="K21" s="5"/>
       <c r="L21" s="5"/>
     </row>
@@ -1322,18 +1322,18 @@
         <v>18</v>
       </c>
       <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="3" t="s">
+      <c r="E22" s="3" t="s">
         <v>30</v>
       </c>
+      <c r="F22" s="3"/>
       <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="1" t="s">
+      <c r="H22" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J22" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I22" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J22" s="5"/>
       <c r="K22" s="5"/>
       <c r="L22" s="5"/>
     </row>
@@ -1345,18 +1345,18 @@
         <v>18</v>
       </c>
       <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="5" t="s">
+      <c r="E23" s="5" t="s">
         <v>31</v>
       </c>
+      <c r="F23" s="5"/>
       <c r="G23" s="5"/>
-      <c r="H23" s="5"/>
-      <c r="I23" s="6" t="s">
+      <c r="H23" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="J23" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I23" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J23" s="5"/>
       <c r="K23" s="5"/>
       <c r="L23" s="5"/>
     </row>
@@ -1368,18 +1368,18 @@
         <v>18</v>
       </c>
       <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="3" t="s">
+      <c r="E24" s="3" t="s">
         <v>32</v>
       </c>
+      <c r="F24" s="3"/>
       <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="1" t="s">
+      <c r="H24" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J24" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I24" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J24" s="5"/>
       <c r="K24" s="5"/>
       <c r="L24" s="5"/>
     </row>
@@ -1391,18 +1391,18 @@
         <v>18</v>
       </c>
       <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="5" t="s">
+      <c r="E25" s="5" t="s">
         <v>33</v>
       </c>
+      <c r="F25" s="5"/>
       <c r="G25" s="5"/>
-      <c r="H25" s="5"/>
-      <c r="I25" s="6" t="s">
+      <c r="H25" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="J25" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I25" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J25" s="5"/>
       <c r="K25" s="5"/>
       <c r="L25" s="5"/>
     </row>
@@ -1414,18 +1414,18 @@
         <v>18</v>
       </c>
       <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="3" t="s">
+      <c r="E26" s="3" t="s">
         <v>34</v>
       </c>
+      <c r="F26" s="3"/>
       <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="1" t="s">
+      <c r="H26" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J26" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I26" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J26" s="3"/>
       <c r="K26" s="3"/>
       <c r="L26" s="3"/>
     </row>
@@ -1437,18 +1437,18 @@
         <v>18</v>
       </c>
       <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="5" t="s">
+      <c r="E27" s="5" t="s">
         <v>35</v>
       </c>
+      <c r="F27" s="5"/>
       <c r="G27" s="5"/>
-      <c r="H27" s="5"/>
-      <c r="I27" s="6" t="s">
+      <c r="H27" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="J27" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I27" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J27" s="3"/>
       <c r="K27" s="3"/>
       <c r="L27" s="3"/>
     </row>
@@ -1460,18 +1460,18 @@
         <v>18</v>
       </c>
       <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="3" t="s">
+      <c r="E28" s="3" t="s">
         <v>36</v>
       </c>
+      <c r="F28" s="3"/>
       <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="1" t="s">
+      <c r="H28" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J28" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I28" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J28" s="5"/>
       <c r="K28" s="5"/>
       <c r="L28" s="5"/>
     </row>
@@ -1483,18 +1483,18 @@
         <v>18</v>
       </c>
       <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="5" t="s">
+      <c r="E29" s="5" t="s">
         <v>37</v>
       </c>
+      <c r="F29" s="5"/>
       <c r="G29" s="5"/>
-      <c r="H29" s="5"/>
-      <c r="I29" s="6" t="s">
+      <c r="H29" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J29" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I29" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J29" s="5"/>
       <c r="K29" s="5"/>
       <c r="L29" s="5"/>
     </row>
@@ -1506,18 +1506,18 @@
         <v>38</v>
       </c>
       <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="3" t="s">
+      <c r="E30" s="3" t="s">
         <v>39</v>
       </c>
+      <c r="F30" s="3"/>
       <c r="G30" s="3"/>
-      <c r="H30" s="3"/>
-      <c r="I30" s="1" t="s">
+      <c r="H30" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J30" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I30" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J30" s="5"/>
       <c r="K30" s="5"/>
       <c r="L30" s="5"/>
     </row>
@@ -1529,18 +1529,18 @@
         <v>40</v>
       </c>
       <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="5" t="s">
+      <c r="E31" s="5" t="s">
         <v>41</v>
       </c>
+      <c r="F31" s="5"/>
       <c r="G31" s="5"/>
-      <c r="H31" s="5"/>
-      <c r="I31" s="6" t="s">
+      <c r="H31" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J31" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I31" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J31" s="5"/>
       <c r="K31" s="5"/>
       <c r="L31" s="5"/>
     </row>
@@ -1552,18 +1552,18 @@
         <v>18</v>
       </c>
       <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="3" t="s">
+      <c r="E32" s="3" t="s">
         <v>42</v>
       </c>
+      <c r="F32" s="3"/>
       <c r="G32" s="3"/>
-      <c r="H32" s="3"/>
-      <c r="I32" s="1" t="s">
+      <c r="H32" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J32" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I32" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J32" s="5"/>
       <c r="K32" s="5"/>
       <c r="L32" s="5"/>
     </row>
@@ -1575,18 +1575,18 @@
         <v>38</v>
       </c>
       <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="5" t="s">
+      <c r="E33" s="5" t="s">
         <v>43</v>
       </c>
+      <c r="F33" s="5"/>
       <c r="G33" s="5"/>
-      <c r="H33" s="5"/>
-      <c r="I33" s="6" t="s">
+      <c r="H33" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J33" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I33" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J33" s="5"/>
       <c r="K33" s="5"/>
       <c r="L33" s="5"/>
     </row>
@@ -1598,18 +1598,18 @@
         <v>40</v>
       </c>
       <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="3" t="s">
+      <c r="E34" s="3" t="s">
         <v>41</v>
       </c>
+      <c r="F34" s="3"/>
       <c r="G34" s="3"/>
-      <c r="H34" s="3"/>
-      <c r="I34" s="1" t="s">
+      <c r="H34" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J34" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I34" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J34" s="5"/>
       <c r="K34" s="5"/>
       <c r="L34" s="5"/>
     </row>
@@ -1621,18 +1621,18 @@
         <v>18</v>
       </c>
       <c r="D35" s="7"/>
-      <c r="E35" s="7"/>
-      <c r="F35" s="5" t="s">
+      <c r="E35" s="5" t="s">
         <v>42</v>
       </c>
+      <c r="F35" s="5"/>
       <c r="G35" s="5"/>
-      <c r="H35" s="5"/>
-      <c r="I35" s="6" t="s">
+      <c r="H35" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="J35" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I35" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J35" s="5"/>
       <c r="K35" s="5"/>
       <c r="L35" s="5"/>
     </row>
@@ -1644,18 +1644,18 @@
         <v>38</v>
       </c>
       <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="3" t="s">
+      <c r="E36" s="3" t="s">
         <v>44</v>
       </c>
+      <c r="F36" s="3"/>
       <c r="G36" s="3"/>
-      <c r="H36" s="3"/>
-      <c r="I36" s="1" t="s">
+      <c r="H36" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J36" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I36" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J36" s="5"/>
       <c r="K36" s="5"/>
       <c r="L36" s="5"/>
     </row>
@@ -1667,18 +1667,18 @@
         <v>40</v>
       </c>
       <c r="D37" s="7"/>
-      <c r="E37" s="7"/>
-      <c r="F37" s="5" t="s">
+      <c r="E37" s="5" t="s">
         <v>45</v>
       </c>
+      <c r="F37" s="5"/>
       <c r="G37" s="5"/>
-      <c r="H37" s="5"/>
-      <c r="I37" s="6" t="s">
+      <c r="H37" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J37" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I37" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J37" s="5"/>
       <c r="K37" s="5"/>
       <c r="L37" s="5"/>
     </row>
@@ -1690,18 +1690,18 @@
         <v>40</v>
       </c>
       <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="3" t="s">
+      <c r="E38" s="3" t="s">
         <v>46</v>
       </c>
+      <c r="F38" s="3"/>
       <c r="G38" s="3"/>
-      <c r="H38" s="3"/>
-      <c r="I38" s="1" t="s">
+      <c r="H38" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J38" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I38" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J38" s="5"/>
       <c r="K38" s="5"/>
       <c r="L38" s="5"/>
     </row>
@@ -1713,18 +1713,18 @@
         <v>40</v>
       </c>
       <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
-      <c r="F39" s="5" t="s">
+      <c r="E39" s="5" t="s">
         <v>47</v>
       </c>
+      <c r="F39" s="5"/>
       <c r="G39" s="5"/>
-      <c r="H39" s="5"/>
-      <c r="I39" s="6" t="s">
+      <c r="H39" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J39" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I39" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J39" s="5"/>
       <c r="K39" s="5"/>
       <c r="L39" s="5"/>
     </row>
@@ -1736,18 +1736,18 @@
         <v>40</v>
       </c>
       <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="3" t="s">
+      <c r="E40" s="3" t="s">
         <v>48</v>
       </c>
+      <c r="F40" s="3"/>
       <c r="G40" s="3"/>
-      <c r="H40" s="3"/>
-      <c r="I40" s="1" t="s">
+      <c r="H40" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J40" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I40" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J40" s="5"/>
       <c r="K40" s="5"/>
       <c r="L40" s="5"/>
     </row>
@@ -1759,18 +1759,18 @@
         <v>18</v>
       </c>
       <c r="D41" s="7"/>
-      <c r="E41" s="7"/>
-      <c r="F41" s="5" t="s">
+      <c r="E41" s="5" t="s">
         <v>49</v>
       </c>
+      <c r="F41" s="5"/>
       <c r="G41" s="5"/>
-      <c r="H41" s="5"/>
-      <c r="I41" s="6" t="s">
+      <c r="H41" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J41" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I41" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J41" s="5"/>
       <c r="K41" s="5"/>
       <c r="L41" s="5"/>
     </row>
@@ -1782,18 +1782,18 @@
         <v>18</v>
       </c>
       <c r="D42" s="2"/>
-      <c r="E42" s="2"/>
-      <c r="F42" s="3" t="s">
+      <c r="E42" s="3" t="s">
         <v>50</v>
       </c>
+      <c r="F42" s="3"/>
       <c r="G42" s="3"/>
-      <c r="H42" s="3"/>
-      <c r="I42" s="1" t="s">
+      <c r="H42" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J42" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I42" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J42" s="5"/>
       <c r="K42" s="5"/>
       <c r="L42" s="5"/>
     </row>
@@ -1805,18 +1805,18 @@
         <v>18</v>
       </c>
       <c r="D43" s="7"/>
-      <c r="E43" s="7"/>
-      <c r="F43" s="5" t="s">
+      <c r="E43" s="5" t="s">
         <v>51</v>
       </c>
+      <c r="F43" s="5"/>
       <c r="G43" s="5"/>
-      <c r="H43" s="5"/>
-      <c r="I43" s="6" t="s">
+      <c r="H43" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J43" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I43" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J43" s="3"/>
       <c r="K43" s="3"/>
       <c r="L43" s="3"/>
     </row>
@@ -1828,18 +1828,18 @@
         <v>52</v>
       </c>
       <c r="D44" s="2"/>
-      <c r="E44" s="2"/>
-      <c r="F44" s="3" t="s">
+      <c r="E44" s="3" t="s">
         <v>53</v>
       </c>
+      <c r="F44" s="3"/>
       <c r="G44" s="3"/>
-      <c r="H44" s="3"/>
-      <c r="I44" s="1" t="s">
+      <c r="H44" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J44" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I44" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J44" s="3"/>
       <c r="K44" s="3"/>
       <c r="L44" s="3"/>
     </row>
@@ -1851,18 +1851,18 @@
         <v>52</v>
       </c>
       <c r="D45" s="7"/>
-      <c r="E45" s="7"/>
-      <c r="F45" s="5" t="s">
+      <c r="E45" s="5" t="s">
         <v>54</v>
       </c>
+      <c r="F45" s="5"/>
       <c r="G45" s="5"/>
-      <c r="H45" s="5"/>
-      <c r="I45" s="6" t="s">
+      <c r="H45" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J45" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I45" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J45" s="3"/>
       <c r="K45" s="3"/>
       <c r="L45" s="3"/>
     </row>
@@ -1874,18 +1874,18 @@
         <v>52</v>
       </c>
       <c r="D46" s="2"/>
-      <c r="E46" s="2"/>
-      <c r="F46" s="3" t="s">
+      <c r="E46" s="3" t="s">
         <v>55</v>
       </c>
+      <c r="F46" s="3"/>
       <c r="G46" s="3"/>
-      <c r="H46" s="3"/>
-      <c r="I46" s="1" t="s">
+      <c r="H46" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J46" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I46" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J46" s="3"/>
       <c r="K46" s="3"/>
       <c r="L46" s="3"/>
     </row>
@@ -1897,18 +1897,18 @@
         <v>52</v>
       </c>
       <c r="D47" s="7"/>
-      <c r="E47" s="7"/>
-      <c r="F47" s="5" t="s">
+      <c r="E47" s="5" t="s">
         <v>56</v>
       </c>
+      <c r="F47" s="5"/>
       <c r="G47" s="5"/>
-      <c r="H47" s="5"/>
-      <c r="I47" s="6" t="s">
+      <c r="H47" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J47" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I47" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J47" s="3"/>
       <c r="K47" s="3"/>
       <c r="L47" s="3"/>
     </row>
@@ -1920,18 +1920,18 @@
         <v>52</v>
       </c>
       <c r="D48" s="2"/>
-      <c r="E48" s="2"/>
-      <c r="F48" s="3" t="s">
+      <c r="E48" s="3" t="s">
         <v>57</v>
       </c>
+      <c r="F48" s="3"/>
       <c r="G48" s="3"/>
-      <c r="H48" s="3"/>
-      <c r="I48" s="1" t="s">
+      <c r="H48" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J48" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I48" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J48" s="5"/>
       <c r="K48" s="5"/>
       <c r="L48" s="5"/>
     </row>
@@ -1943,18 +1943,18 @@
         <v>52</v>
       </c>
       <c r="D49" s="7"/>
-      <c r="E49" s="7"/>
-      <c r="F49" s="5" t="s">
+      <c r="E49" s="5" t="s">
         <v>58</v>
       </c>
+      <c r="F49" s="5"/>
       <c r="G49" s="5"/>
-      <c r="H49" s="5"/>
-      <c r="I49" s="6" t="s">
+      <c r="H49" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="J49" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I49" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J49" s="3"/>
       <c r="K49" s="3"/>
       <c r="L49" s="3"/>
     </row>
@@ -1966,18 +1966,18 @@
         <v>52</v>
       </c>
       <c r="D50" s="2"/>
-      <c r="E50" s="2"/>
-      <c r="F50" s="3" t="s">
+      <c r="E50" s="3" t="s">
         <v>59</v>
       </c>
+      <c r="F50" s="3"/>
       <c r="G50" s="3"/>
-      <c r="H50" s="3"/>
-      <c r="I50" s="1" t="s">
+      <c r="H50" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J50" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I50" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J50" s="5"/>
       <c r="K50" s="5"/>
       <c r="L50" s="5"/>
     </row>
@@ -1989,18 +1989,18 @@
         <v>52</v>
       </c>
       <c r="D51" s="7"/>
-      <c r="E51" s="7"/>
-      <c r="F51" s="5" t="s">
+      <c r="E51" s="5" t="s">
         <v>60</v>
       </c>
+      <c r="F51" s="5"/>
       <c r="G51" s="5"/>
-      <c r="H51" s="5"/>
-      <c r="I51" s="1" t="s">
+      <c r="H51" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J51" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I51" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J51" s="5"/>
       <c r="K51" s="5"/>
       <c r="L51" s="5"/>
     </row>
@@ -2012,18 +2012,18 @@
         <v>61</v>
       </c>
       <c r="D52" s="2"/>
-      <c r="E52" s="2"/>
-      <c r="F52" s="3" t="s">
+      <c r="E52" s="3" t="s">
         <v>62</v>
       </c>
+      <c r="F52" s="3"/>
       <c r="G52" s="3"/>
-      <c r="H52" s="3"/>
-      <c r="I52" s="1" t="s">
+      <c r="H52" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J52" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I52" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J52" s="5"/>
       <c r="K52" s="5"/>
       <c r="L52" s="5"/>
     </row>
@@ -2035,18 +2035,18 @@
         <v>61</v>
       </c>
       <c r="D53" s="7"/>
-      <c r="E53" s="7"/>
-      <c r="F53" s="5" t="s">
+      <c r="E53" s="5" t="s">
         <v>63</v>
       </c>
+      <c r="F53" s="5"/>
       <c r="G53" s="5"/>
-      <c r="H53" s="5"/>
-      <c r="I53" s="6" t="s">
+      <c r="H53" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J53" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I53" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J53" s="5"/>
       <c r="K53" s="5"/>
       <c r="L53" s="5"/>
     </row>
@@ -2058,18 +2058,18 @@
         <v>61</v>
       </c>
       <c r="D54" s="2"/>
-      <c r="E54" s="2"/>
-      <c r="F54" s="3" t="s">
+      <c r="E54" s="3" t="s">
         <v>64</v>
       </c>
+      <c r="F54" s="3"/>
       <c r="G54" s="3"/>
-      <c r="H54" s="3"/>
-      <c r="I54" s="1" t="s">
+      <c r="H54" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J54" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I54" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J54" s="5"/>
       <c r="K54" s="5"/>
       <c r="L54" s="5"/>
     </row>
@@ -2081,18 +2081,18 @@
         <v>61</v>
       </c>
       <c r="D55" s="7"/>
-      <c r="E55" s="7"/>
-      <c r="F55" s="5" t="s">
+      <c r="E55" s="5" t="s">
         <v>65</v>
       </c>
+      <c r="F55" s="5"/>
       <c r="G55" s="5"/>
-      <c r="H55" s="5"/>
-      <c r="I55" s="6" t="s">
+      <c r="H55" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="J55" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I55" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J55" s="5"/>
       <c r="K55" s="5"/>
       <c r="L55" s="5"/>
     </row>
@@ -2104,18 +2104,18 @@
         <v>61</v>
       </c>
       <c r="D56" s="2"/>
-      <c r="E56" s="2"/>
-      <c r="F56" s="3" t="s">
+      <c r="E56" s="3" t="s">
         <v>66</v>
       </c>
+      <c r="F56" s="3"/>
       <c r="G56" s="3"/>
-      <c r="H56" s="3"/>
-      <c r="I56" s="1" t="s">
+      <c r="H56" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J56" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I56" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J56" s="5"/>
       <c r="K56" s="5"/>
       <c r="L56" s="5"/>
     </row>
@@ -2127,18 +2127,18 @@
         <v>61</v>
       </c>
       <c r="D57" s="7"/>
-      <c r="E57" s="7"/>
-      <c r="F57" s="5" t="s">
+      <c r="E57" s="5" t="s">
         <v>67</v>
       </c>
+      <c r="F57" s="5"/>
       <c r="G57" s="5"/>
-      <c r="H57" s="5"/>
-      <c r="I57" s="6" t="s">
+      <c r="H57" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J57" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I57" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J57" s="5"/>
       <c r="K57" s="5"/>
       <c r="L57" s="5"/>
     </row>
@@ -2150,18 +2150,18 @@
         <v>61</v>
       </c>
       <c r="D58" s="2"/>
-      <c r="E58" s="2"/>
-      <c r="F58" s="3" t="s">
+      <c r="E58" s="3" t="s">
         <v>68</v>
       </c>
+      <c r="F58" s="3"/>
       <c r="G58" s="3"/>
-      <c r="H58" s="3"/>
-      <c r="I58" s="1" t="s">
+      <c r="H58" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J58" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I58" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J58" s="5"/>
       <c r="K58" s="5"/>
       <c r="L58" s="5"/>
     </row>
@@ -2173,18 +2173,18 @@
         <v>61</v>
       </c>
       <c r="D59" s="7"/>
-      <c r="E59" s="7"/>
-      <c r="F59" s="5" t="s">
+      <c r="E59" s="5" t="s">
         <v>69</v>
       </c>
+      <c r="F59" s="5"/>
       <c r="G59" s="5"/>
-      <c r="H59" s="5"/>
-      <c r="I59" s="6" t="s">
+      <c r="H59" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J59" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I59" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J59" s="5"/>
       <c r="K59" s="5"/>
       <c r="L59" s="5"/>
     </row>
@@ -2196,18 +2196,18 @@
         <v>61</v>
       </c>
       <c r="D60" s="2"/>
-      <c r="E60" s="2"/>
-      <c r="F60" s="3" t="s">
+      <c r="E60" s="3" t="s">
         <v>70</v>
       </c>
+      <c r="F60" s="3"/>
       <c r="G60" s="3"/>
-      <c r="H60" s="3"/>
-      <c r="I60" s="1" t="s">
+      <c r="H60" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J60" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I60" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J60" s="5"/>
       <c r="K60" s="5"/>
       <c r="L60" s="5"/>
     </row>
@@ -2219,18 +2219,18 @@
         <v>61</v>
       </c>
       <c r="D61" s="7"/>
-      <c r="E61" s="7"/>
-      <c r="F61" s="5" t="s">
+      <c r="E61" s="5" t="s">
         <v>71</v>
       </c>
+      <c r="F61" s="5"/>
       <c r="G61" s="5"/>
-      <c r="H61" s="5"/>
-      <c r="I61" s="6" t="s">
+      <c r="H61" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="J61" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I61" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J61" s="5"/>
       <c r="K61" s="5"/>
       <c r="L61" s="5"/>
     </row>
@@ -2242,18 +2242,18 @@
         <v>61</v>
       </c>
       <c r="D62" s="2"/>
-      <c r="E62" s="2"/>
-      <c r="F62" s="3" t="s">
+      <c r="E62" s="3" t="s">
         <v>72</v>
       </c>
+      <c r="F62" s="3"/>
       <c r="G62" s="3"/>
-      <c r="H62" s="3"/>
-      <c r="I62" s="1" t="s">
+      <c r="H62" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J62" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I62" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J62" s="5"/>
       <c r="K62" s="5"/>
       <c r="L62" s="5"/>
     </row>
@@ -2265,18 +2265,18 @@
         <v>73</v>
       </c>
       <c r="D63" s="7"/>
-      <c r="E63" s="7"/>
-      <c r="F63" s="5" t="s">
+      <c r="E63" s="5" t="s">
         <v>74</v>
       </c>
+      <c r="F63" s="5"/>
       <c r="G63" s="5"/>
-      <c r="H63" s="5"/>
-      <c r="I63" s="6" t="s">
+      <c r="H63" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J63" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I63" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J63" s="5"/>
       <c r="K63" s="5"/>
       <c r="L63" s="5"/>
     </row>
@@ -2288,18 +2288,18 @@
         <v>73</v>
       </c>
       <c r="D64" s="2"/>
-      <c r="E64" s="2"/>
-      <c r="F64" s="3" t="s">
+      <c r="E64" s="3" t="s">
         <v>75</v>
       </c>
+      <c r="F64" s="3"/>
       <c r="G64" s="3"/>
-      <c r="H64" s="3"/>
-      <c r="I64" s="1" t="s">
+      <c r="H64" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J64" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I64" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J64" s="5"/>
       <c r="K64" s="5"/>
       <c r="L64" s="5"/>
     </row>
@@ -2311,18 +2311,18 @@
         <v>73</v>
       </c>
       <c r="D65" s="7"/>
-      <c r="E65" s="7"/>
-      <c r="F65" s="5" t="s">
+      <c r="E65" s="5" t="s">
         <v>76</v>
       </c>
+      <c r="F65" s="5"/>
       <c r="G65" s="5"/>
-      <c r="H65" s="5"/>
-      <c r="I65" s="6" t="s">
+      <c r="H65" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J65" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I65" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J65" s="5"/>
       <c r="K65" s="5"/>
       <c r="L65" s="5"/>
     </row>
@@ -2334,18 +2334,18 @@
         <v>73</v>
       </c>
       <c r="D66" s="2"/>
-      <c r="E66" s="2"/>
-      <c r="F66" s="3" t="s">
+      <c r="E66" s="3" t="s">
         <v>77</v>
       </c>
+      <c r="F66" s="3"/>
       <c r="G66" s="3"/>
-      <c r="H66" s="3"/>
-      <c r="I66" s="1" t="s">
+      <c r="H66" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J66" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I66" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J66" s="5"/>
       <c r="K66" s="5"/>
       <c r="L66" s="5"/>
     </row>
@@ -2357,18 +2357,18 @@
         <v>73</v>
       </c>
       <c r="D67" s="7"/>
-      <c r="E67" s="7"/>
-      <c r="F67" s="5" t="s">
+      <c r="E67" s="5" t="s">
         <v>78</v>
       </c>
+      <c r="F67" s="5"/>
       <c r="G67" s="5"/>
-      <c r="H67" s="5"/>
-      <c r="I67" s="6" t="s">
+      <c r="H67" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J67" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I67" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J67" s="5"/>
       <c r="K67" s="5"/>
       <c r="L67" s="5"/>
     </row>
@@ -2380,18 +2380,18 @@
         <v>73</v>
       </c>
       <c r="D68" s="2"/>
-      <c r="E68" s="2"/>
-      <c r="F68" s="3" t="s">
+      <c r="E68" s="3" t="s">
         <v>79</v>
       </c>
+      <c r="F68" s="3"/>
       <c r="G68" s="3"/>
-      <c r="H68" s="3"/>
-      <c r="I68" s="1" t="s">
+      <c r="H68" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J68" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I68" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J68" s="5"/>
       <c r="K68" s="5"/>
       <c r="L68" s="5"/>
     </row>
@@ -2403,18 +2403,18 @@
         <v>73</v>
       </c>
       <c r="D69" s="7"/>
-      <c r="E69" s="7"/>
-      <c r="F69" s="5" t="s">
+      <c r="E69" s="5" t="s">
         <v>80</v>
       </c>
+      <c r="F69" s="5"/>
       <c r="G69" s="5"/>
-      <c r="H69" s="5"/>
-      <c r="I69" s="1" t="s">
+      <c r="H69" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J69" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I69" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J69" s="5"/>
       <c r="K69" s="5"/>
       <c r="L69" s="5"/>
     </row>
@@ -2426,18 +2426,18 @@
         <v>73</v>
       </c>
       <c r="D70" s="2"/>
-      <c r="E70" s="2"/>
-      <c r="F70" s="3" t="s">
+      <c r="E70" s="3" t="s">
         <v>81</v>
       </c>
+      <c r="F70" s="3"/>
       <c r="G70" s="3"/>
-      <c r="H70" s="3"/>
-      <c r="I70" s="1" t="s">
+      <c r="H70" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J70" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I70" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J70" s="5"/>
       <c r="K70" s="5"/>
       <c r="L70" s="5"/>
     </row>
@@ -2449,18 +2449,18 @@
         <v>73</v>
       </c>
       <c r="D71" s="7"/>
-      <c r="E71" s="7"/>
-      <c r="F71" s="5" t="s">
+      <c r="E71" s="5" t="s">
         <v>82</v>
       </c>
+      <c r="F71" s="5"/>
       <c r="G71" s="5"/>
-      <c r="H71" s="5"/>
-      <c r="I71" s="6" t="s">
+      <c r="H71" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="J71" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I71" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J71" s="5"/>
       <c r="K71" s="5"/>
       <c r="L71" s="5"/>
     </row>
@@ -2472,18 +2472,18 @@
         <v>73</v>
       </c>
       <c r="D72" s="2"/>
-      <c r="E72" s="2"/>
-      <c r="F72" s="3" t="s">
+      <c r="E72" s="3" t="s">
         <v>83</v>
       </c>
+      <c r="F72" s="3"/>
       <c r="G72" s="3"/>
-      <c r="H72" s="3"/>
-      <c r="I72" s="1" t="s">
+      <c r="H72" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J72" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I72" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J72" s="5"/>
       <c r="K72" s="5"/>
       <c r="L72" s="5"/>
     </row>
@@ -2495,18 +2495,18 @@
         <v>73</v>
       </c>
       <c r="D73" s="7"/>
-      <c r="E73" s="7"/>
-      <c r="F73" s="5" t="s">
+      <c r="E73" s="5" t="s">
         <v>84</v>
       </c>
+      <c r="F73" s="5"/>
       <c r="G73" s="5"/>
-      <c r="H73" s="5"/>
-      <c r="I73" s="6" t="s">
+      <c r="H73" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="J73" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I73" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J73" s="5"/>
       <c r="K73" s="5"/>
       <c r="L73" s="5"/>
     </row>
@@ -2518,18 +2518,18 @@
         <v>73</v>
       </c>
       <c r="D74" s="2"/>
-      <c r="E74" s="2"/>
-      <c r="F74" s="3" t="s">
+      <c r="E74" s="3" t="s">
         <v>85</v>
       </c>
+      <c r="F74" s="3"/>
       <c r="G74" s="3"/>
-      <c r="H74" s="3"/>
-      <c r="I74" s="1" t="s">
+      <c r="H74" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J74" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I74" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J74" s="5"/>
       <c r="K74" s="5"/>
       <c r="L74" s="5"/>
     </row>
@@ -2541,18 +2541,18 @@
         <v>73</v>
       </c>
       <c r="D75" s="7"/>
-      <c r="E75" s="7"/>
-      <c r="F75" s="5" t="s">
+      <c r="E75" s="5" t="s">
         <v>86</v>
       </c>
+      <c r="F75" s="5"/>
       <c r="G75" s="5"/>
-      <c r="H75" s="5"/>
-      <c r="I75" s="6" t="s">
+      <c r="H75" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="J75" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I75" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J75" s="5"/>
       <c r="K75" s="5"/>
       <c r="L75" s="5"/>
     </row>
@@ -2564,18 +2564,18 @@
         <v>73</v>
       </c>
       <c r="D76" s="2"/>
-      <c r="E76" s="2"/>
-      <c r="F76" s="3" t="s">
+      <c r="E76" s="3" t="s">
         <v>87</v>
       </c>
+      <c r="F76" s="3"/>
       <c r="G76" s="3"/>
-      <c r="H76" s="3"/>
-      <c r="I76" s="1" t="s">
+      <c r="H76" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J76" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I76" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J76" s="5"/>
       <c r="K76" s="5"/>
       <c r="L76" s="5"/>
     </row>
@@ -2587,18 +2587,18 @@
         <v>88</v>
       </c>
       <c r="D77" s="7"/>
-      <c r="E77" s="7"/>
-      <c r="F77" s="5" t="s">
+      <c r="E77" s="5" t="s">
         <v>89</v>
       </c>
+      <c r="F77" s="5"/>
       <c r="G77" s="5"/>
-      <c r="H77" s="5"/>
-      <c r="I77" s="6" t="s">
+      <c r="H77" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="J77" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I77" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J77" s="5"/>
       <c r="K77" s="5"/>
       <c r="L77" s="5"/>
     </row>
@@ -2610,18 +2610,18 @@
         <v>88</v>
       </c>
       <c r="D78" s="2"/>
-      <c r="E78" s="2"/>
-      <c r="F78" s="3" t="s">
+      <c r="E78" s="3" t="s">
         <v>90</v>
       </c>
+      <c r="F78" s="3"/>
       <c r="G78" s="3"/>
-      <c r="H78" s="3"/>
-      <c r="I78" s="1" t="s">
+      <c r="H78" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J78" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I78" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J78" s="5"/>
       <c r="K78" s="5"/>
       <c r="L78" s="5"/>
     </row>
@@ -2633,18 +2633,18 @@
         <v>88</v>
       </c>
       <c r="D79" s="7"/>
-      <c r="E79" s="7"/>
-      <c r="F79" s="5" t="s">
+      <c r="E79" s="5" t="s">
         <v>91</v>
       </c>
+      <c r="F79" s="5"/>
       <c r="G79" s="5"/>
-      <c r="H79" s="5"/>
-      <c r="I79" s="6" t="s">
+      <c r="H79" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="J79" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I79" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J79" s="5"/>
       <c r="K79" s="5"/>
       <c r="L79" s="5"/>
     </row>
@@ -2656,18 +2656,18 @@
         <v>88</v>
       </c>
       <c r="D80" s="2"/>
-      <c r="E80" s="2"/>
-      <c r="F80" s="3" t="s">
+      <c r="E80" s="3" t="s">
         <v>92</v>
       </c>
+      <c r="F80" s="3"/>
       <c r="G80" s="3"/>
-      <c r="H80" s="3"/>
-      <c r="I80" s="1" t="s">
+      <c r="H80" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J80" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I80" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J80" s="5"/>
       <c r="K80" s="5"/>
       <c r="L80" s="5"/>
     </row>
@@ -2679,18 +2679,18 @@
         <v>88</v>
       </c>
       <c r="D81" s="7"/>
-      <c r="E81" s="7"/>
-      <c r="F81" s="5" t="s">
+      <c r="E81" s="5" t="s">
         <v>93</v>
       </c>
+      <c r="F81" s="5"/>
       <c r="G81" s="5"/>
-      <c r="H81" s="5"/>
-      <c r="I81" s="6" t="s">
+      <c r="H81" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="J81" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I81" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J81" s="5"/>
       <c r="K81" s="5"/>
       <c r="L81" s="5"/>
     </row>
@@ -2702,18 +2702,18 @@
         <v>88</v>
       </c>
       <c r="D82" s="2"/>
-      <c r="E82" s="2"/>
-      <c r="F82" s="3" t="s">
+      <c r="E82" s="3" t="s">
         <v>94</v>
       </c>
+      <c r="F82" s="3"/>
       <c r="G82" s="3"/>
-      <c r="H82" s="3"/>
-      <c r="I82" s="1" t="s">
+      <c r="H82" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J82" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I82" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J82" s="5"/>
       <c r="K82" s="5"/>
       <c r="L82" s="5"/>
     </row>
@@ -2725,18 +2725,18 @@
         <v>95</v>
       </c>
       <c r="D83" s="7"/>
-      <c r="E83" s="7"/>
-      <c r="F83" s="5" t="s">
+      <c r="E83" s="5" t="s">
         <v>96</v>
       </c>
+      <c r="F83" s="5"/>
       <c r="G83" s="5"/>
-      <c r="H83" s="5"/>
-      <c r="I83" s="6" t="s">
+      <c r="H83" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J83" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I83" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J83" s="5"/>
       <c r="K83" s="5"/>
       <c r="L83" s="5"/>
     </row>
@@ -2748,18 +2748,18 @@
         <v>95</v>
       </c>
       <c r="D84" s="2"/>
-      <c r="E84" s="2"/>
-      <c r="F84" s="3" t="s">
+      <c r="E84" s="3" t="s">
         <v>97</v>
       </c>
+      <c r="F84" s="3"/>
       <c r="G84" s="3"/>
-      <c r="H84" s="3"/>
-      <c r="I84" s="1" t="s">
+      <c r="H84" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J84" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I84" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J84" s="5"/>
       <c r="K84" s="5"/>
       <c r="L84" s="5"/>
     </row>
@@ -2771,18 +2771,18 @@
         <v>95</v>
       </c>
       <c r="D85" s="7"/>
-      <c r="E85" s="7"/>
-      <c r="F85" s="5" t="s">
+      <c r="E85" s="5" t="s">
         <v>98</v>
       </c>
+      <c r="F85" s="5"/>
       <c r="G85" s="5"/>
-      <c r="H85" s="5"/>
-      <c r="I85" s="6" t="s">
+      <c r="H85" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J85" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I85" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J85" s="5"/>
       <c r="K85" s="5"/>
       <c r="L85" s="5"/>
     </row>
@@ -2794,18 +2794,18 @@
         <v>95</v>
       </c>
       <c r="D86" s="2"/>
-      <c r="E86" s="2"/>
-      <c r="F86" s="3" t="s">
+      <c r="E86" s="3" t="s">
         <v>99</v>
       </c>
+      <c r="F86" s="3"/>
       <c r="G86" s="3"/>
-      <c r="H86" s="3"/>
-      <c r="I86" s="1" t="s">
+      <c r="H86" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J86" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I86" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J86" s="5"/>
       <c r="K86" s="5"/>
       <c r="L86" s="5"/>
     </row>
@@ -2817,18 +2817,18 @@
         <v>95</v>
       </c>
       <c r="D87" s="7"/>
-      <c r="E87" s="7"/>
-      <c r="F87" s="5" t="s">
+      <c r="E87" s="5" t="s">
         <v>100</v>
       </c>
+      <c r="F87" s="5"/>
       <c r="G87" s="5"/>
-      <c r="H87" s="5"/>
-      <c r="I87" s="6" t="s">
+      <c r="H87" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J87" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I87" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J87" s="5"/>
       <c r="K87" s="5"/>
       <c r="L87" s="5"/>
     </row>
@@ -2840,18 +2840,18 @@
         <v>52</v>
       </c>
       <c r="D88" s="2"/>
-      <c r="E88" s="2"/>
-      <c r="F88" s="3" t="s">
+      <c r="E88" s="3" t="s">
         <v>101</v>
       </c>
+      <c r="F88" s="3"/>
       <c r="G88" s="3"/>
-      <c r="H88" s="3"/>
-      <c r="I88" s="1" t="s">
+      <c r="H88" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J88" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I88" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J88" s="5"/>
       <c r="K88" s="5"/>
       <c r="L88" s="5"/>
     </row>
@@ -2863,18 +2863,18 @@
         <v>52</v>
       </c>
       <c r="D89" s="7"/>
-      <c r="E89" s="7"/>
-      <c r="F89" s="5" t="s">
+      <c r="E89" s="5" t="s">
         <v>102</v>
       </c>
+      <c r="F89" s="5"/>
       <c r="G89" s="5"/>
-      <c r="H89" s="5"/>
-      <c r="I89" s="6" t="s">
+      <c r="H89" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="J89" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I89" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J89" s="5"/>
       <c r="K89" s="5"/>
       <c r="L89" s="5"/>
     </row>
@@ -2886,18 +2886,18 @@
         <v>4</v>
       </c>
       <c r="D90" s="2"/>
-      <c r="E90" s="2"/>
-      <c r="F90" s="3" t="s">
+      <c r="E90" s="3" t="s">
         <v>103</v>
       </c>
+      <c r="F90" s="3"/>
       <c r="G90" s="3"/>
-      <c r="H90" s="3"/>
-      <c r="I90" s="1" t="s">
+      <c r="H90" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J90" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="I90" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J90" s="5"/>
       <c r="K90" s="5"/>
       <c r="L90" s="5"/>
     </row>
@@ -7080,21 +7080,21 @@
       <c r="I1048" s="8"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="J2:J248">
+  <conditionalFormatting sqref="J91:J248 I2:I90">
     <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="Funciona">
-      <formula>NOT(ISERROR(SEARCH("Funciona",J2)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Funciona",I2)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="Falla">
-      <formula>NOT(ISERROR(SEARCH("Falla",J2)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Falla",I2)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text="N/A">
-      <formula>NOT(ISERROR(SEARCH("N/A",J2)))</formula>
+      <formula>NOT(ISERROR(SEARCH("N/A",I2)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="1" priority="5" operator="containsText" text="Pendiente">
-      <formula>NOT(ISERROR(SEARCH("Pendiente",J2)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Pendiente",I2)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="0" priority="6" operator="containsText" text="Por ejecutar">
-      <formula>NOT(ISERROR(SEARCH("Por ejecutar",J2)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Por ejecutar",I2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
@@ -7102,7 +7102,7 @@
       <formula1>"Acceso,Buscador,Control Compras,Control Parental,Navegación,NPVR,Perfiles,Rep. Canal Líneal,Reproducción,TimeShift,Transacción,Claro Música,Trickplay,Social y Settings"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="J2:J234 J236" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="J236 I2:I90 J91:J234" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Funciona,Falla nueva,Falla persiste,N/A,Pendiente,Por ejecutar,"</formula1>
       <formula2>0</formula2>
     </dataValidation>
